--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,59 +634,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₹6,499.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,15 +634,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,59 +634,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₹6,499.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,15 +634,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,59 +634,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₹6,499.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,117 +497,117 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,32 +617,76 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>₹599.00</t>
+          <t>₹799.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,117 +497,117 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,76 +617,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₹6,499.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,15 +634,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,59 +634,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₹6,499.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,15 +634,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,117 +497,117 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,32 +617,76 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,59 +634,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₹6,499.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,117 +497,117 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,32 +617,76 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,17 +612,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>ENIGMA OF TAIF 100ml</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
         </is>
       </c>
     </row>
@@ -634,17 +634,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -661,32 +661,10 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,17 +612,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,17 +634,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>ENIGMA OF TAIF 100ml</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
         </is>
       </c>
     </row>
@@ -661,10 +661,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,117 +497,117 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,76 +617,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₹6,499.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,15 +634,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,59 +634,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₹6,499.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,15 +634,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,117 +497,117 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,32 +617,76 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,59 +634,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₹6,499.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,15 +634,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,117 +497,117 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,76 +617,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₹6,499.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,15 +634,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,117 +497,117 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,76 +617,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₹6,499.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,15 +634,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,117 +497,117 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,76 +617,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₹6,499.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,15 +634,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,59 +634,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₹6,499.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,59 +634,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₹6,499.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,117 +497,117 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,051.00 (was ₹4,949.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,32 +617,76 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,051.00 (was ₹4,949.00)</t>
+          <t>₹4,151.00 (was ₹4,849.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹4,151.00 (was ₹4,849.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,151.00 (was ₹4,849.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,59 +634,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₹6,499.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹4,151.00 (was ₹4,849.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,151.00 (was ₹4,849.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,15 +634,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹4,151.00 (was ₹4,849.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,151.00 (was ₹4,849.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,59 +634,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₹6,499.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹4,151.00 (was ₹4,849.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,151.00 (was ₹4,849.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,15 +634,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,17 +458,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5.0 / 5.0 5.0 (7)</t>
+          <t>Decant/Sample 10ml Swiss Arabian Enigma of Taif for Men &amp; Women</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>₹5.00 (was ₹7.00)</t>
+          <t>₹799.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum#shopify-product-reviews</t>
+          <t>https://perfumeaddiction.com/products/decant-sample-10ml-swiss-arabian-enigma-of-taif-for-men-women</t>
         </is>
       </c>
     </row>
@@ -480,17 +480,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Decant/Sample 10ml Swiss Arabian Enigma of Taif for Men &amp; Women</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>₹799.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/decant-sample-10ml-swiss-arabian-enigma-of-taif-for-men-women</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹4,151.00 (was ₹4,849.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,151.00 (was ₹4,849.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -612,17 +612,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>ENIGMA OF TAIF 100ml</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
         </is>
       </c>
     </row>
@@ -634,61 +634,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₹6,499.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
           <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,17 +458,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Decant/Sample 10ml Swiss Arabian Enigma of Taif for Men &amp; Women</t>
+          <t>5.0 / 5.0 5.0 (7)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>₹799.00</t>
+          <t>₹5.00 (was ₹7.00)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/decant-sample-10ml-swiss-arabian-enigma-of-taif-for-men-women</t>
+          <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum#shopify-product-reviews</t>
         </is>
       </c>
     </row>
@@ -480,17 +480,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample 10ml Swiss Arabian Enigma of Taif for Men &amp; Women</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹799.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumeaddiction.com/products/decant-sample-10ml-swiss-arabian-enigma-of-taif-for-men-women</t>
         </is>
       </c>
     </row>
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹4,151.00 (was ₹4,849.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,151.00 (was ₹4,849.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -612,17 +612,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,17 +634,61 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>₹6,499.00</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹4,151.00 (was ₹4,849.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,151.00 (was ₹4,849.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,59 +634,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₹6,499.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹4,151.00 (was ₹4,849.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,151.00 (was ₹4,849.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,15 +634,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -546,7 +546,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 1 review price Save</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 2 reviews price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 2 reviews price Save</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹4,151.00 (was ₹4,849.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 2 reviews price Save</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,151.00 (was ₹4,849.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,59 +634,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₹6,499.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 2 reviews price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹4,151.00 (was ₹4,849.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 2 reviews price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,151.00 (was ₹4,849.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,15 +634,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 2 reviews price Save</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹4,151.00 (was ₹4,849.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 2 reviews price Save</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,151.00 (was ₹4,849.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -634,59 +634,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₹6,499.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,117 +497,117 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 2 reviews price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹4,151.00 (was ₹4,849.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 2 reviews price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,151.00 (was ₹4,849.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -617,32 +617,76 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,250.00 (was ₹9,900.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -480,17 +480,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Decant/Sample 10ml Swiss Arabian Enigma of Taif for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum 5ml</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>₹799.00</t>
+          <t>₹465.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/decant-sample-10ml-swiss-arabian-enigma-of-taif-for-men-women</t>
+          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -502,17 +502,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample 10ml Swiss Arabian Enigma of Taif for Men &amp; Women</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹799.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumeaddiction.com/products/decant-sample-10ml-swiss-arabian-enigma-of-taif-for-men-women</t>
         </is>
       </c>
     </row>
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 2 reviews price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,151.00 (was ₹4,849.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 2 reviews price Save</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,151.00 (was ₹4,849.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -612,17 +612,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,250.00 (was ₹9,900.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://scentira.in/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,174 +519,130 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 10ml Decant</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹800.00 (was ₹1,000.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 2 reviews price Save</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹4,151.00 (was ₹4,849.00)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 2 reviews price Save</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,151.00 (was ₹4,849.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹6,499.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENIGMA OF TAIF 100ml</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₹5,350.00 (was ₹5,550.00)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>₹6,499.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,17 +524,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
+          <t>ENIGMA OF TAIF 10ml Decant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₹899.00</t>
+          <t>₹800.00 (was ₹1,000.00)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-10ml-decant</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 2 reviews price Save</t>
+          <t>Decant/Sample Of Swiss Arabian Enigma Of Taif Extrait De Parfum 10ml For Man &amp; Woman No reviews</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₹4,151.00 (was ₹4,849.00)</t>
+          <t>₹899.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/decant-sample-of-swiss-arabian-enigma-of-taif-extrait-de-parfum-10ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -568,17 +568,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
+          <t>Swiss Arabian Enigma Of Taif Extrait De Parfum 100ml For Man &amp; Woman 2 reviews price Save</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₹4,999.00 (was ₹8,950.00)</t>
+          <t>₹4,151.00 (was ₹4,849.00)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumepalace.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum-100ml-for-man-woman</t>
         </is>
       </c>
     </row>
@@ -590,17 +590,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum Unisex</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₹5,199.00 (was ₹6,500.00)</t>
+          <t>₹4,999.00 (was ₹8,950.00)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
+          <t>https://belvish.com/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>
       </c>
     </row>
@@ -612,17 +612,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+          <t>Swiss Arabian Enigma of Taif 100ml EDP for Men &amp; Women</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₹6,499.00</t>
+          <t>₹5,199.00 (was ₹6,500.00)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+          <t>https://perfumeaddiction.com/products/swiss-arabian-enigma-of-taif-100ml-edp-for-men-women</t>
         </is>
       </c>
     </row>
@@ -634,15 +634,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>ENIGMA OF TAIF 100ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₹5,350.00 (was ₹5,550.00)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.naazperfumes.com/product/enigma-of-taif-100ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₹6,499.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://perfumex.in/collections/swiss-arabian-perfumes/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Swiss Arabian Enigma of Taif Extrait de Parfum</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.perfumenetwork.in/collections/swiss-arabian/products/swiss-arabian-enigma-of-taif-extrait-de-parfum</t>
         </is>

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/daily_offers.xlsx
+++ b/daily_offers.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
